--- a/outputs/52305.xlsx
+++ b/outputs/52305.xlsx
@@ -189,44 +189,48 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -483,848 +487,848 @@
   <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="10.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="10.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>44396.9088078704</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="E2" s="2"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>44389.8400694444</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="G3" s="6" t="s">
+      <c r="E3" s="6"/>
+      <c r="G3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6" t="n">
+      <c r="H3" s="7"/>
+      <c r="I3" s="7" t="n">
         <v>155</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="J3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44396.7485532407</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44396.7521875</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="M5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="N5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44396.763912037</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>268</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="9" t="n">
         <v>0.541666666666667</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="I6" s="9" t="n">
         <v>0.5625</v>
       </c>
-      <c r="J6" s="0" t="n">
+      <c r="J6" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H6)*(MOD($B$2:$B$15,1)&lt;=$I6))</f>
         <v>0</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H6)*(MOD($B$2:$B$15,1)&lt;=$I6))</f>
         <v>0</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H6)*(MOD($B$2:$B$15,1)&lt;=$I6))</f>
         <v>0</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H6)*(MOD($B$2:$B$15,1)&lt;=$I6))</f>
         <v>0</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H6)*(MOD($B$2:$B$15,1)&lt;=$I6))</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44396.9096643519</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>268</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="9" t="n">
         <v>0.5625</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="9" t="n">
         <v>0.583333333333333</v>
       </c>
-      <c r="J7" s="0" t="n">
+      <c r="J7" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H7)*(MOD($B$2:$B$15,1)&lt;=$I7))</f>
         <v>0</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H7)*(MOD($B$2:$B$15,1)&lt;=$I7))</f>
         <v>0</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H7)*(MOD($B$2:$B$15,1)&lt;=$I7))</f>
         <v>0</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H7)*(MOD($B$2:$B$15,1)&lt;=$I7))</f>
         <v>0</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H7)*(MOD($B$2:$B$15,1)&lt;=$I7))</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>44390.8242708333</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="9" t="n">
         <v>0.583333333333333</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="9" t="n">
         <v>0.604166666666667</v>
       </c>
-      <c r="J8" s="0" t="n">
+      <c r="J8" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H8)*(MOD($B$2:$B$15,1)&lt;=$I8))</f>
         <v>0</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H8)*(MOD($B$2:$B$15,1)&lt;=$I8))</f>
         <v>0</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H8)*(MOD($B$2:$B$15,1)&lt;=$I8))</f>
         <v>0</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H8)*(MOD($B$2:$B$15,1)&lt;=$I8))</f>
         <v>0</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H8)*(MOD($B$2:$B$15,1)&lt;=$I8))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44390.9107407407</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H9" s="9" t="n">
         <v>0.604166666666667</v>
       </c>
-      <c r="I9" s="8" t="n">
+      <c r="I9" s="9" t="n">
         <v>0.625</v>
       </c>
-      <c r="J9" s="0" t="n">
+      <c r="J9" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H9)*(MOD($B$2:$B$15,1)&lt;=$I9))</f>
         <v>0</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H9)*(MOD($B$2:$B$15,1)&lt;=$I9))</f>
         <v>0</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H9)*(MOD($B$2:$B$15,1)&lt;=$I9))</f>
         <v>0</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H9)*(MOD($B$2:$B$15,1)&lt;=$I9))</f>
         <v>0</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H9)*(MOD($B$2:$B$15,1)&lt;=$I9))</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44392.582037037</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H10" s="9" t="n">
         <v>0.625</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="I10" s="9" t="n">
         <v>0.645833333333333</v>
       </c>
-      <c r="J10" s="0" t="n">
+      <c r="J10" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H10)*(MOD($B$2:$B$15,1)&lt;=$I10))</f>
         <v>0</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H10)*(MOD($B$2:$B$15,1)&lt;=$I10))</f>
         <v>0</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H10)*(MOD($B$2:$B$15,1)&lt;=$I10))</f>
         <v>0</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H10)*(MOD($B$2:$B$15,1)&lt;=$I10))</f>
         <v>0</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H10)*(MOD($B$2:$B$15,1)&lt;=$I10))</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44391.8942592593</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="9" t="n">
         <v>0.645833333333333</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I11" s="9" t="n">
         <v>0.666666666666667</v>
       </c>
-      <c r="J11" s="0" t="n">
+      <c r="J11" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H11)*(MOD($B$2:$B$15,1)&lt;=$I11))</f>
         <v>0</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H11)*(MOD($B$2:$B$15,1)&lt;=$I11))</f>
         <v>0</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H11)*(MOD($B$2:$B$15,1)&lt;=$I11))</f>
         <v>0</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H11)*(MOD($B$2:$B$15,1)&lt;=$I11))</f>
         <v>0</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H11)*(MOD($B$2:$B$15,1)&lt;=$I11))</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>44389.8400694444</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="9" t="n">
         <v>0.666666666666667</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="I12" s="9" t="n">
         <v>0.6875</v>
       </c>
-      <c r="J12" s="0" t="n">
+      <c r="J12" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H12)*(MOD($B$2:$B$15,1)&lt;=$I12))</f>
         <v>0</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H12)*(MOD($B$2:$B$15,1)&lt;=$I12))</f>
         <v>0</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H12)*(MOD($B$2:$B$15,1)&lt;=$I12))</f>
         <v>0</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H12)*(MOD($B$2:$B$15,1)&lt;=$I12))</f>
         <v>0</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H12)*(MOD($B$2:$B$15,1)&lt;=$I12))</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>44389.8400694444</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="9" t="n">
         <v>0.6875</v>
       </c>
-      <c r="I13" s="8" t="n">
+      <c r="I13" s="9" t="n">
         <v>0.708333333333333</v>
       </c>
-      <c r="J13" s="0" t="n">
+      <c r="J13" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H13)*(MOD($B$2:$B$15,1)&lt;=$I13))</f>
         <v>0</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H13)*(MOD($B$2:$B$15,1)&lt;=$I13))</f>
         <v>0</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H13)*(MOD($B$2:$B$15,1)&lt;=$I13))</f>
         <v>0</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H13)*(MOD($B$2:$B$15,1)&lt;=$I13))</f>
         <v>0</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H13)*(MOD($B$2:$B$15,1)&lt;=$I13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>44389.8400694444</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="9" t="n">
         <v>0.708333333333333</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I14" s="9" t="n">
         <v>0.729166666666667</v>
       </c>
-      <c r="J14" s="0" t="n">
+      <c r="J14" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H14)*(MOD($B$2:$B$15,1)&lt;=$I14))</f>
         <v>0</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="K14" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H14)*(MOD($B$2:$B$15,1)&lt;=$I14))</f>
         <v>0</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H14)*(MOD($B$2:$B$15,1)&lt;=$I14))</f>
         <v>0</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H14)*(MOD($B$2:$B$15,1)&lt;=$I14))</f>
         <v>0</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H14)*(MOD($B$2:$B$15,1)&lt;=$I14))</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>44389.8400694444</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="9" t="n">
         <v>0.729166666666667</v>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="9" t="n">
         <v>0.75</v>
       </c>
-      <c r="J15" s="0" t="n">
+      <c r="J15" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H15)*(MOD($B$2:$B$15,1)&lt;=$I15))</f>
         <v>0</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="K15" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H15)*(MOD($B$2:$B$15,1)&lt;=$I15))</f>
         <v>1</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H15)*(MOD($B$2:$B$15,1)&lt;=$I15))</f>
         <v>0</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H15)*(MOD($B$2:$B$15,1)&lt;=$I15))</f>
         <v>0</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H15)*(MOD($B$2:$B$15,1)&lt;=$I15))</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="9"/>
-      <c r="H16" s="8" t="n">
+      <c r="B16" s="10"/>
+      <c r="H16" s="9" t="n">
         <v>0.75</v>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="I16" s="9" t="n">
         <v>0.770833333333333</v>
       </c>
-      <c r="J16" s="0" t="n">
+      <c r="J16" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H16)*(MOD($B$2:$B$15,1)&lt;=$I16))</f>
         <v>0</v>
       </c>
-      <c r="K16" s="0" t="n">
+      <c r="K16" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H16)*(MOD($B$2:$B$15,1)&lt;=$I16))</f>
         <v>1</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="L16" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H16)*(MOD($B$2:$B$15,1)&lt;=$I16))</f>
         <v>1</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H16)*(MOD($B$2:$B$15,1)&lt;=$I16))</f>
         <v>0</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H16)*(MOD($B$2:$B$15,1)&lt;=$I16))</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="9"/>
-      <c r="H17" s="8" t="n">
+      <c r="B17" s="10"/>
+      <c r="H17" s="9" t="n">
         <v>0.770833333333333</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="I17" s="9" t="n">
         <v>0.791666666666667</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J17" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H17)*(MOD($B$2:$B$15,1)&lt;=$I17))</f>
         <v>0</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H17)*(MOD($B$2:$B$15,1)&lt;=$I17))</f>
         <v>0</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H17)*(MOD($B$2:$B$15,1)&lt;=$I17))</f>
         <v>0</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H17)*(MOD($B$2:$B$15,1)&lt;=$I17))</f>
         <v>0</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H17)*(MOD($B$2:$B$15,1)&lt;=$I17))</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="9"/>
-      <c r="H18" s="8" t="n">
+      <c r="B18" s="10"/>
+      <c r="H18" s="9" t="n">
         <v>0.791666666666667</v>
       </c>
-      <c r="I18" s="8" t="n">
+      <c r="I18" s="9" t="n">
         <v>0.8125</v>
       </c>
-      <c r="J18" s="0" t="n">
+      <c r="J18" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H18)*(MOD($B$2:$B$15,1)&lt;=$I18))</f>
         <v>0</v>
       </c>
-      <c r="K18" s="0" t="n">
+      <c r="K18" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H18)*(MOD($B$2:$B$15,1)&lt;=$I18))</f>
         <v>0</v>
       </c>
-      <c r="L18" s="0" t="n">
+      <c r="L18" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H18)*(MOD($B$2:$B$15,1)&lt;=$I18))</f>
         <v>0</v>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="M18" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H18)*(MOD($B$2:$B$15,1)&lt;=$I18))</f>
         <v>0</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H18)*(MOD($B$2:$B$15,1)&lt;=$I18))</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="9"/>
-      <c r="H19" s="8" t="n">
+      <c r="B19" s="10"/>
+      <c r="H19" s="9" t="n">
         <v>0.8125</v>
       </c>
-      <c r="I19" s="8" t="n">
+      <c r="I19" s="9" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="J19" s="0" t="n">
+      <c r="J19" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H19)*(MOD($B$2:$B$15,1)&lt;=$I19))</f>
         <v>1</v>
       </c>
-      <c r="K19" s="0" t="n">
+      <c r="K19" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H19)*(MOD($B$2:$B$15,1)&lt;=$I19))</f>
         <v>0</v>
       </c>
-      <c r="L19" s="0" t="n">
+      <c r="L19" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H19)*(MOD($B$2:$B$15,1)&lt;=$I19))</f>
         <v>0</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H19)*(MOD($B$2:$B$15,1)&lt;=$I19))</f>
         <v>0</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H19)*(MOD($B$2:$B$15,1)&lt;=$I19))</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9"/>
-      <c r="H20" s="8" t="n">
+      <c r="B20" s="10"/>
+      <c r="H20" s="9" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="I20" s="8" t="n">
+      <c r="I20" s="9" t="n">
         <v>0.854166666666667</v>
       </c>
-      <c r="J20" s="0" t="n">
+      <c r="J20" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H20)*(MOD($B$2:$B$15,1)&lt;=$I20))</f>
         <v>3</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="K20" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H20)*(MOD($B$2:$B$15,1)&lt;=$I20))</f>
         <v>0</v>
       </c>
-      <c r="L20" s="0" t="n">
+      <c r="L20" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H20)*(MOD($B$2:$B$15,1)&lt;=$I20))</f>
         <v>1</v>
       </c>
-      <c r="M20" s="0" t="n">
+      <c r="M20" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H20)*(MOD($B$2:$B$15,1)&lt;=$I20))</f>
         <v>0</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H20)*(MOD($B$2:$B$15,1)&lt;=$I20))</f>
         <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9"/>
-      <c r="H21" s="8" t="n">
+      <c r="B21" s="10"/>
+      <c r="H21" s="9" t="n">
         <v>0.854166666666667</v>
       </c>
-      <c r="I21" s="8" t="n">
+      <c r="I21" s="9" t="n">
         <v>0.875</v>
       </c>
-      <c r="J21" s="0" t="n">
+      <c r="J21" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H21)*(MOD($B$2:$B$15,1)&lt;=$I21))</f>
         <v>0</v>
       </c>
-      <c r="K21" s="0" t="n">
+      <c r="K21" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H21)*(MOD($B$2:$B$15,1)&lt;=$I21))</f>
         <v>0</v>
       </c>
-      <c r="L21" s="0" t="n">
+      <c r="L21" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H21)*(MOD($B$2:$B$15,1)&lt;=$I21))</f>
         <v>0</v>
       </c>
-      <c r="M21" s="0" t="n">
+      <c r="M21" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H21)*(MOD($B$2:$B$15,1)&lt;=$I21))</f>
         <v>0</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H21)*(MOD($B$2:$B$15,1)&lt;=$I21))</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="9"/>
-      <c r="H22" s="8" t="n">
+      <c r="B22" s="10"/>
+      <c r="H22" s="9" t="n">
         <v>0.875</v>
       </c>
-      <c r="I22" s="8" t="n">
+      <c r="I22" s="9" t="n">
         <v>0.895833333333333</v>
       </c>
-      <c r="J22" s="0" t="n">
+      <c r="J22" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H22)*(MOD($B$2:$B$15,1)&lt;=$I22))</f>
         <v>0</v>
       </c>
-      <c r="K22" s="0" t="n">
+      <c r="K22" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H22)*(MOD($B$2:$B$15,1)&lt;=$I22))</f>
         <v>1</v>
       </c>
-      <c r="L22" s="0" t="n">
+      <c r="L22" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H22)*(MOD($B$2:$B$15,1)&lt;=$I22))</f>
         <v>0</v>
       </c>
-      <c r="M22" s="0" t="n">
+      <c r="M22" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H22)*(MOD($B$2:$B$15,1)&lt;=$I22))</f>
         <v>0</v>
       </c>
-      <c r="N22" s="0" t="n">
+      <c r="N22" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H22)*(MOD($B$2:$B$15,1)&lt;=$I22))</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="9"/>
-      <c r="H23" s="8" t="n">
+      <c r="B23" s="10"/>
+      <c r="H23" s="9" t="n">
         <v>0.895833333333333</v>
       </c>
-      <c r="I23" s="8" t="n">
+      <c r="I23" s="9" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="J23" s="0" t="n">
+      <c r="J23" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H23)*(MOD($B$2:$B$15,1)&lt;=$I23))</f>
         <v>1</v>
       </c>
-      <c r="K23" s="0" t="n">
+      <c r="K23" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H23)*(MOD($B$2:$B$15,1)&lt;=$I23))</f>
         <v>0</v>
       </c>
-      <c r="L23" s="0" t="n">
+      <c r="L23" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H23)*(MOD($B$2:$B$15,1)&lt;=$I23))</f>
         <v>1</v>
       </c>
-      <c r="M23" s="0" t="n">
+      <c r="M23" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H23)*(MOD($B$2:$B$15,1)&lt;=$I23))</f>
         <v>1</v>
       </c>
-      <c r="N23" s="0" t="n">
+      <c r="N23" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H23)*(MOD($B$2:$B$15,1)&lt;=$I23))</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9"/>
-      <c r="H24" s="8" t="n">
+      <c r="B24" s="10"/>
+      <c r="H24" s="9" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="I24" s="8" t="n">
+      <c r="I24" s="9" t="n">
         <v>0.9375</v>
       </c>
-      <c r="J24" s="0" t="n">
+      <c r="J24" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=J$5)*(MOD($B$2:$B$15,1)&gt;=$H24)*(MOD($B$2:$B$15,1)&lt;=$I24))</f>
         <v>0</v>
       </c>
-      <c r="K24" s="0" t="n">
+      <c r="K24" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=K$5)*(MOD($B$2:$B$15,1)&gt;=$H24)*(MOD($B$2:$B$15,1)&lt;=$I24))</f>
         <v>0</v>
       </c>
-      <c r="L24" s="0" t="n">
+      <c r="L24" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=L$5)*(MOD($B$2:$B$15,1)&gt;=$H24)*(MOD($B$2:$B$15,1)&lt;=$I24))</f>
         <v>0</v>
       </c>
-      <c r="M24" s="0" t="n">
+      <c r="M24" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=M$5)*(MOD($B$2:$B$15,1)&gt;=$H24)*(MOD($B$2:$B$15,1)&lt;=$I24))</f>
         <v>0</v>
       </c>
-      <c r="N24" s="0" t="n">
+      <c r="N24" s="1" t="n">
         <f aca="false">SUMPRODUCT(($C$2:$C$15=N$5)*(MOD($B$2:$B$15,1)&gt;=$H24)*(MOD($B$2:$B$15,1)&lt;=$I24))</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="9"/>
+      <c r="B25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="9"/>
-      <c r="H26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="H26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="9"/>
-      <c r="H27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="H27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="9"/>
-      <c r="H28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="H28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="9"/>
-      <c r="H29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="H29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="9"/>
-      <c r="H30" s="9"/>
+      <c r="B30" s="10"/>
+      <c r="H30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="9"/>
-      <c r="H31" s="9"/>
+      <c r="B31" s="10"/>
+      <c r="H31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="9"/>
-      <c r="H32" s="9"/>
+      <c r="B32" s="10"/>
+      <c r="H32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="9"/>
-      <c r="H33" s="9"/>
+      <c r="B33" s="10"/>
+      <c r="H33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="9"/>
-      <c r="H34" s="9"/>
+      <c r="B34" s="10"/>
+      <c r="H34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="9"/>
+      <c r="B35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="9"/>
+      <c r="B36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="9"/>
+      <c r="B37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="9"/>
+      <c r="B38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="9"/>
+      <c r="B39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="9"/>
+      <c r="B40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="9"/>
+      <c r="B41" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
